--- a/imports/Elemento.xlsx
+++ b/imports/Elemento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD46490F-18E1-4F7F-B617-FBFA74BACB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD363E0-FF5E-4573-9AAE-EF3365F0A518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elemento" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="336">
   <si>
     <t>EL</t>
   </si>
@@ -834,12 +834,6 @@
   </si>
   <si>
     <t>FR-SA-001</t>
-  </si>
-  <si>
-    <t>FR-SA-002</t>
-  </si>
-  <si>
-    <t>FR-SA-003</t>
   </si>
   <si>
     <t>Elementos Sacudir</t>
@@ -1214,7 +1208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1274,6 +1268,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1303,21 +1300,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2312,30 +2294,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
       <c r="J1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="22"/>
-      <c r="O1" s="21" t="s">
+      <c r="M1" s="23"/>
+      <c r="O1" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="21"/>
+      <c r="P1" s="22"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
@@ -3412,11 +3394,11 @@
       <c r="J29" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="L29" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="M29" s="31" t="s">
-        <v>290</v>
+      <c r="L29" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3450,11 +3432,11 @@
       <c r="J30" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="L30" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="M30" s="31" t="s">
-        <v>303</v>
+      <c r="L30" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3488,10 +3470,10 @@
       <c r="J31" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="L31" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="M31" s="31" t="s">
+      <c r="L31" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3721,7 +3703,7 @@
     </row>
     <row r="39" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>174</v>
@@ -3753,7 +3735,7 @@
     </row>
     <row r="40" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>174</v>
@@ -3785,7 +3767,7 @@
     </row>
     <row r="41" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>174</v>
@@ -3816,8 +3798,8 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="31" t="s">
-        <v>284</v>
+      <c r="A42" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>175</v>
@@ -3832,7 +3814,7 @@
         <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>0</v>
@@ -3840,16 +3822,16 @@
       <c r="H42" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I42" s="32" t="s">
-        <v>286</v>
+      <c r="I42" s="21" t="s">
+        <v>284</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>175</v>
@@ -3876,7 +3858,7 @@
         <v>4</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
@@ -3896,7 +3878,7 @@
         <v>28</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>0</v>
@@ -3912,40 +3894,40 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="31" t="s">
-        <v>291</v>
+      <c r="A45" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D45" s="31">
+        <v>287</v>
+      </c>
+      <c r="D45" s="1">
         <v>1</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="33" t="s">
-        <v>292</v>
+      <c r="F45" s="10" t="s">
+        <v>290</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H45" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="I45" s="34">
+      <c r="H45" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I45" s="11">
         <v>1</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="31" t="s">
-        <v>294</v>
+      <c r="A46" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>175</v>
@@ -3953,7 +3935,7 @@
       <c r="C46" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="1">
         <v>1</v>
       </c>
       <c r="E46" s="10" t="s">
@@ -3968,8 +3950,8 @@
       <c r="H46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I46" s="32" t="s">
-        <v>286</v>
+      <c r="I46" s="21" t="s">
+        <v>284</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>182</v>
@@ -3977,7 +3959,7 @@
     </row>
     <row r="47" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>175</v>
@@ -3997,19 +3979,19 @@
       <c r="G47" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H47" s="31" t="s">
+      <c r="H47" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I47" s="32" t="s">
-        <v>286</v>
+      <c r="I47" s="21" t="s">
+        <v>284</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="31" t="s">
-        <v>296</v>
+      <c r="A48" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>175</v>
@@ -4017,31 +3999,31 @@
       <c r="C48" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="1">
         <v>3</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F48" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="G48" s="31" t="s">
+      <c r="F48" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H48" s="31" t="s">
+      <c r="H48" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I48" s="34">
+      <c r="I48" s="11">
         <v>2</v>
       </c>
-      <c r="J48" s="31" t="s">
-        <v>298</v>
+      <c r="J48" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>175</v>
@@ -4058,22 +4040,22 @@
       <c r="F49" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="G49" s="31" t="s">
+      <c r="G49" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I49" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="J49" s="31" t="s">
-        <v>301</v>
+      <c r="I49" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>175</v>
@@ -4090,49 +4072,49 @@
       <c r="F50" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G50" s="31" t="s">
+      <c r="G50" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I50" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="J50" s="31" t="s">
+      <c r="I50" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="31" t="s">
-        <v>304</v>
+      <c r="A51" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D51" s="31">
+        <v>300</v>
+      </c>
+      <c r="D51" s="1">
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="33" t="s">
+      <c r="F51" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I51" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="G51" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H51" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="I51" s="35" t="s">
-        <v>306</v>
-      </c>
-      <c r="J51" s="31" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
@@ -4168,8 +4150,8 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="31" t="s">
-        <v>308</v>
+      <c r="A53" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>175</v>
@@ -4177,7 +4159,7 @@
       <c r="C53" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="1">
         <v>4</v>
       </c>
       <c r="E53" s="10" t="s">
@@ -4186,54 +4168,54 @@
       <c r="F53" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H53" s="31" t="s">
+      <c r="H53" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I53" s="35" t="s">
+      <c r="I53" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="J53" s="31" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="28.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="31" t="s">
-        <v>311</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D54" s="31">
+        <v>308</v>
+      </c>
+      <c r="D54" s="1">
         <v>1</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="F54" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I54" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="G54" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H54" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="I54" s="35" t="s">
-        <v>306</v>
-      </c>
-      <c r="J54" s="31" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="31" t="s">
-        <v>314</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>175</v>
@@ -4241,7 +4223,7 @@
       <c r="C55" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="10" t="s">
@@ -4250,22 +4232,22 @@
       <c r="F55" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H55" s="31" t="s">
+      <c r="H55" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I55" s="35" t="s">
+      <c r="I55" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="J55" s="31" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="31" t="s">
-        <v>317</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>175</v>
@@ -4273,31 +4255,31 @@
       <c r="C56" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F56" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="G56" s="31" t="s">
+      <c r="F56" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H56" s="31" t="s">
+      <c r="H56" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I56" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="J56" s="31" t="s">
-        <v>319</v>
+      <c r="I56" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>175</v>
@@ -4329,7 +4311,7 @@
     </row>
     <row r="58" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>175</v>
@@ -4361,7 +4343,7 @@
     </row>
     <row r="59" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>175</v>
@@ -4393,7 +4375,7 @@
     </row>
     <row r="60" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>176</v>
@@ -4416,8 +4398,8 @@
       <c r="H60" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I60" s="32" t="s">
-        <v>315</v>
+      <c r="I60" s="21" t="s">
+        <v>313</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>39</v>
@@ -4425,7 +4407,7 @@
     </row>
     <row r="61" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>176</v>
@@ -4448,8 +4430,8 @@
       <c r="H61" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="I61" s="32" t="s">
-        <v>315</v>
+      <c r="I61" s="21" t="s">
+        <v>313</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>244</v>
@@ -4472,7 +4454,7 @@
         <v>28</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>0</v>
@@ -4480,11 +4462,11 @@
       <c r="H62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I62" s="32" t="s">
-        <v>309</v>
+      <c r="I62" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -4504,7 +4486,7 @@
         <v>28</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>0</v>
@@ -4521,7 +4503,7 @@
     </row>
     <row r="64" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>176</v>
@@ -4544,8 +4526,8 @@
       <c r="H64" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="I64" s="32" t="s">
-        <v>309</v>
+      <c r="I64" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>247</v>
@@ -4553,7 +4535,7 @@
     </row>
     <row r="65" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>176</v>
@@ -4576,8 +4558,8 @@
       <c r="H65" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I65" s="32" t="s">
-        <v>309</v>
+      <c r="I65" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>181</v>
@@ -4585,7 +4567,7 @@
     </row>
     <row r="66" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>176</v>
@@ -4608,16 +4590,16 @@
       <c r="H66" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I66" s="32" t="s">
-        <v>329</v>
+      <c r="I66" s="21" t="s">
+        <v>327</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A67" s="31" t="s">
-        <v>330</v>
+      <c r="A67" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>176</v>
@@ -4625,7 +4607,7 @@
       <c r="C67" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D67" s="31">
+      <c r="D67" s="1">
         <v>1</v>
       </c>
       <c r="E67" s="10" t="s">
@@ -4634,22 +4616,22 @@
       <c r="F67" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G67" s="31" t="s">
+      <c r="G67" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H67" s="31" t="s">
+      <c r="H67" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I67" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="J67" s="31" t="s">
-        <v>316</v>
+      <c r="I67" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>176</v>
@@ -4681,7 +4663,7 @@
     </row>
     <row r="69" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>176</v>
@@ -4698,22 +4680,22 @@
       <c r="F69" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G69" s="31" t="s">
+      <c r="G69" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I69" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="J69" s="31" t="s">
+      <c r="I69" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>176</v>
@@ -4745,7 +4727,7 @@
     </row>
     <row r="71" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>176</v>
@@ -4776,8 +4758,8 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="31" t="s">
-        <v>335</v>
+      <c r="A72" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>176</v>
@@ -4785,7 +4767,7 @@
       <c r="C72" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="10" t="s">
@@ -4800,8 +4782,8 @@
       <c r="H72" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I72" s="32" t="s">
-        <v>309</v>
+      <c r="I72" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>182</v>
@@ -4809,7 +4791,7 @@
     </row>
     <row r="73" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>176</v>
@@ -4841,7 +4823,7 @@
     </row>
     <row r="74" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>176</v>
@@ -4887,55 +4869,55 @@
     <mergeCell ref="G1:I1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="M3:M31">
-    <cfRule type="duplicateValues" dxfId="92" priority="58"/>
+  <conditionalFormatting sqref="A50">
+    <cfRule type="duplicateValues" dxfId="92" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H49:H51 H53:H56">
-    <cfRule type="duplicateValues" dxfId="91" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="90" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="19"/>
+  <conditionalFormatting sqref="A52 A3:A26 A28:A49 A58:A59">
+    <cfRule type="duplicateValues" dxfId="90" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
     <cfRule type="duplicateValues" dxfId="88" priority="15"/>
     <cfRule type="duplicateValues" dxfId="87" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H67">
-    <cfRule type="duplicateValues" dxfId="86" priority="12"/>
+  <conditionalFormatting sqref="A61 A3:A59 A67:A74">
+    <cfRule type="duplicateValues" dxfId="86" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A68">
     <cfRule type="duplicateValues" dxfId="85" priority="10"/>
     <cfRule type="duplicateValues" dxfId="84" priority="11"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" dxfId="83" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A70:A71">
-    <cfRule type="duplicateValues" dxfId="83" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H69">
-    <cfRule type="duplicateValues" dxfId="81" priority="7"/>
+  <conditionalFormatting sqref="A72">
+    <cfRule type="duplicateValues" dxfId="79" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="80" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52 A3:A26 A28:A49 A58:A59">
-    <cfRule type="duplicateValues" dxfId="78" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="133"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A61 A3:A59 A67:A74">
-    <cfRule type="duplicateValues" dxfId="76" priority="140"/>
+  <conditionalFormatting sqref="A73">
+    <cfRule type="duplicateValues" dxfId="77" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:A160 A3:A74">
     <cfRule type="duplicateValues" dxfId="75" priority="144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A72">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="4"/>
+  <conditionalFormatting sqref="H49:H51 H53:H56">
+    <cfRule type="duplicateValues" dxfId="74" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A73">
-    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="2"/>
+  <conditionalFormatting sqref="H67">
+    <cfRule type="duplicateValues" dxfId="73" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H69">
+    <cfRule type="duplicateValues" dxfId="72" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M31">
+    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4961,33 +4943,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="27" t="s">
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="O1" s="25" t="s">
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="O1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="R1" s="22" t="s">
+      <c r="P1" s="27"/>
+      <c r="R1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="22"/>
+      <c r="S1" s="23"/>
     </row>
     <row r="2" spans="1:19" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
@@ -5564,7 +5546,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>139</v>
@@ -6689,7 +6671,7 @@
         <v>160</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>193</v>
@@ -6703,7 +6685,7 @@
         <v>263</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>212</v>
@@ -6744,7 +6726,7 @@
         <v>263</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>213</v>
@@ -6788,10 +6770,10 @@
         <v>34</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>158</v>
@@ -6815,7 +6797,7 @@
         <v>262</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>199</v>
@@ -6829,10 +6811,10 @@
         <v>242</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>159</v>
@@ -6856,7 +6838,7 @@
         <v>262</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>199</v>
@@ -6870,10 +6852,10 @@
         <v>9</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>159</v>
@@ -6897,7 +6879,7 @@
         <v>262</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>199</v>
@@ -6911,10 +6893,10 @@
         <v>2</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>158</v>
@@ -6938,7 +6920,7 @@
         <v>262</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>199</v>
@@ -6952,7 +6934,7 @@
         <v>8</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="16"/>
@@ -6975,10 +6957,10 @@
         <v>262</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -6989,10 +6971,10 @@
         <v>35</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>158</v>
@@ -7016,7 +6998,7 @@
         <v>262</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>199</v>
@@ -7030,7 +7012,7 @@
         <v>6</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="16"/>
@@ -7053,10 +7035,10 @@
         <v>262</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -7067,10 +7049,10 @@
         <v>258</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>159</v>
@@ -7094,7 +7076,7 @@
         <v>262</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>199</v>
@@ -7105,13 +7087,13 @@
         <v>264</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>159</v>
@@ -7135,7 +7117,7 @@
         <v>262</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>199</v>
@@ -7149,10 +7131,10 @@
         <v>34</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>158</v>
@@ -7176,7 +7158,7 @@
         <v>262</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>199</v>
@@ -7190,10 +7172,10 @@
         <v>242</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>159</v>
@@ -7217,7 +7199,7 @@
         <v>262</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>199</v>
@@ -7231,10 +7213,10 @@
         <v>245</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>158</v>
@@ -7258,7 +7240,7 @@
         <v>262</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>199</v>
@@ -7272,10 +7254,10 @@
         <v>249</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>159</v>
@@ -7299,7 +7281,7 @@
         <v>262</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>199</v>
@@ -7313,13 +7295,13 @@
         <v>238</v>
       </c>
       <c r="C54" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="F54" s="1">
         <v>5</v>
@@ -7340,7 +7322,7 @@
         <v>262</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>199</v>
@@ -7354,10 +7336,10 @@
         <v>9</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>159</v>
@@ -7381,7 +7363,7 @@
         <v>262</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>199</v>
@@ -7395,10 +7377,10 @@
         <v>2</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>158</v>
@@ -7422,7 +7404,7 @@
         <v>262</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>199</v>
@@ -7436,7 +7418,7 @@
         <v>8</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="16"/>
@@ -7459,10 +7441,10 @@
         <v>262</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -7473,10 +7455,10 @@
         <v>35</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>158</v>
@@ -7500,7 +7482,7 @@
         <v>262</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>199</v>
@@ -7514,7 +7496,7 @@
         <v>6</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="16"/>
@@ -7537,10 +7519,10 @@
         <v>262</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -7551,10 +7533,10 @@
         <v>258</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>159</v>
@@ -7578,7 +7560,7 @@
         <v>262</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>199</v>
@@ -7589,13 +7571,13 @@
         <v>265</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>159</v>
@@ -7619,7 +7601,7 @@
         <v>262</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>199</v>
@@ -7633,10 +7615,10 @@
         <v>34</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>158</v>
@@ -7660,7 +7642,7 @@
         <v>262</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M62" s="1" t="s">
         <v>199</v>
@@ -7674,10 +7656,10 @@
         <v>242</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>159</v>
@@ -7701,7 +7683,7 @@
         <v>262</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M63" s="1" t="s">
         <v>199</v>
@@ -7715,10 +7697,10 @@
         <v>245</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>158</v>
@@ -7742,7 +7724,7 @@
         <v>262</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>199</v>
@@ -7756,10 +7738,10 @@
         <v>249</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>159</v>
@@ -7783,7 +7765,7 @@
         <v>262</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>199</v>
@@ -7797,13 +7779,13 @@
         <v>238</v>
       </c>
       <c r="C66" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="F66" s="1">
         <v>5</v>
@@ -7824,7 +7806,7 @@
         <v>262</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>199</v>
@@ -7838,10 +7820,10 @@
         <v>9</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>159</v>
@@ -7865,7 +7847,7 @@
         <v>262</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>199</v>
@@ -7879,10 +7861,10 @@
         <v>2</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>158</v>
@@ -7906,7 +7888,7 @@
         <v>262</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>199</v>
@@ -7920,7 +7902,7 @@
         <v>8</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="16"/>
@@ -7943,10 +7925,10 @@
         <v>262</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -7957,10 +7939,10 @@
         <v>35</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>158</v>
@@ -7984,7 +7966,7 @@
         <v>262</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>199</v>
@@ -7998,7 +7980,7 @@
         <v>6</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="16"/>
@@ -8021,10 +8003,10 @@
         <v>262</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
@@ -8035,10 +8017,10 @@
         <v>258</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>159</v>
@@ -8062,7 +8044,7 @@
         <v>262</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>199</v>
@@ -8076,10 +8058,10 @@
         <v>259</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>159</v>
@@ -8103,7 +8085,7 @@
         <v>262</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>199</v>
@@ -8137,52 +8119,52 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="70" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="68" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="66" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34:B36">
-    <cfRule type="duplicateValues" dxfId="64" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="62" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:B40">
     <cfRule type="duplicateValues" dxfId="60" priority="35"/>
     <cfRule type="duplicateValues" dxfId="59" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41">
-    <cfRule type="duplicateValues" dxfId="58" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="54" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
     <cfRule type="duplicateValues" dxfId="50" priority="43"/>
     <cfRule type="duplicateValues" dxfId="49" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="48" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
     <cfRule type="duplicateValues" dxfId="46" priority="41"/>
@@ -8201,12 +8183,12 @@
     <cfRule type="duplicateValues" dxfId="39" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="38" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="36" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53">
     <cfRule type="duplicateValues" dxfId="34" priority="29"/>
@@ -8221,12 +8203,12 @@
     <cfRule type="duplicateValues" dxfId="29" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B59">
-    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:B61">
-    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62">
     <cfRule type="duplicateValues" dxfId="24" priority="17"/>
@@ -8241,28 +8223,28 @@
     <cfRule type="duplicateValues" dxfId="19" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
     <cfRule type="duplicateValues" dxfId="16" priority="9"/>
     <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:B69">
-    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70:B71">
     <cfRule type="duplicateValues" dxfId="12" priority="5"/>
     <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P8 P10">
     <cfRule type="duplicateValues" dxfId="6" priority="70"/>
@@ -8304,28 +8286,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="28" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="27" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="N1" s="25" t="s">
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="N1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="26"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:15" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="14" t="s">
@@ -8693,7 +8675,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>3</v>
@@ -8711,7 +8693,7 @@
         <v>262</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>161</v>
@@ -8731,13 +8713,13 @@
         <v>174</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>3</v>
@@ -8755,7 +8737,7 @@
         <v>262</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>165</v>
@@ -8775,13 +8757,13 @@
         <v>174</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>3</v>
@@ -8799,7 +8781,7 @@
         <v>262</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>160</v>

--- a/imports/Elemento.xlsx
+++ b/imports/Elemento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3512CC-E64E-471B-A225-2F1CB3C982B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD50905F-762B-4267-94FB-D297CC4063FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="ElementoSet" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Elemento!$A$2:$J$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Elemento!$A$2:$J$239</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -11268,7 +11268,7 @@
     <row r="310" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="311" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A2:J232" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:J239" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:I1"/>

--- a/imports/Elemento.xlsx
+++ b/imports/Elemento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD50905F-762B-4267-94FB-D297CC4063FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25C0FB4-DF00-4EF3-A91E-6C32398CFC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="585">
   <si>
     <t>EL</t>
   </si>
@@ -1656,6 +1656,135 @@
   </si>
   <si>
     <t>EL-CH-015</t>
+  </si>
+  <si>
+    <t>EL-LM-022</t>
+  </si>
+  <si>
+    <t>PD-IN-CO-001</t>
+  </si>
+  <si>
+    <t>EL-BO-015</t>
+  </si>
+  <si>
+    <t>EL-BP-018</t>
+  </si>
+  <si>
+    <t>VIGAS</t>
+  </si>
+  <si>
+    <t>VG</t>
+  </si>
+  <si>
+    <t>EL-VG-001</t>
+  </si>
+  <si>
+    <t>VIGA</t>
+  </si>
+  <si>
+    <t>Viga Techo</t>
+  </si>
+  <si>
+    <t>TU</t>
+  </si>
+  <si>
+    <t>TUBERIA</t>
+  </si>
+  <si>
+    <t>Tuberia Techo</t>
+  </si>
+  <si>
+    <t>EL-TU-001</t>
+  </si>
+  <si>
+    <t>EL-AH-022</t>
+  </si>
+  <si>
+    <t>Mueble Medicamentos</t>
+  </si>
+  <si>
+    <t>EL-MU-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesa Pasteur </t>
+  </si>
+  <si>
+    <t>EL-ME-004</t>
+  </si>
+  <si>
+    <t>Mesa Movil</t>
+  </si>
+  <si>
+    <t>EL-ME-005</t>
+  </si>
+  <si>
+    <t>EL-EC-012</t>
+  </si>
+  <si>
+    <t>EL-SI-015</t>
+  </si>
+  <si>
+    <t>EL-SI-016</t>
+  </si>
+  <si>
+    <t>Silla Madera</t>
+  </si>
+  <si>
+    <t>CAMILLA</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>EL-CA-001</t>
+  </si>
+  <si>
+    <t>Camilla</t>
+  </si>
+  <si>
+    <t>BANQUILLO</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>EL-BN-001</t>
+  </si>
+  <si>
+    <t>Banquillo</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>BASCULA</t>
+  </si>
+  <si>
+    <t>EL-BC-001</t>
+  </si>
+  <si>
+    <t>Bascula</t>
+  </si>
+  <si>
+    <t>EL-LM-023</t>
+  </si>
+  <si>
+    <t>Lampara Examen</t>
+  </si>
+  <si>
+    <t>EL-AR-007</t>
+  </si>
+  <si>
+    <t>Ventilador</t>
+  </si>
+  <si>
+    <t>EL-LZ-018</t>
+  </si>
+  <si>
+    <t>EL-PU-018</t>
+  </si>
+  <si>
+    <t>EL-CH-018</t>
   </si>
 </sst>
 </file>
@@ -1852,7 +1981,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1972,11 +2101,17 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="143">
+  <dxfs count="152">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2003,6 +2138,11 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -2522,11 +2662,44 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2539,6 +2712,18 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -2708,11 +2893,6 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3211,8 +3391,8 @@
     <col min="2" max="2" width="15.73046875" customWidth="1"/>
     <col min="3" max="3" width="15" style="6" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="17.265625" customWidth="1"/>
-    <col min="8" max="8" width="15.3984375" customWidth="1"/>
+    <col min="6" max="6" width="21.73046875" customWidth="1"/>
+    <col min="8" max="8" width="14.265625" customWidth="1"/>
     <col min="9" max="9" width="12.3984375" customWidth="1"/>
     <col min="10" max="10" width="27.86328125" customWidth="1"/>
     <col min="11" max="11" width="6.46484375" customWidth="1"/>
@@ -4590,8 +4770,12 @@
       <c r="J36" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="L36" s="15"/>
-      <c r="M36" s="14"/>
+      <c r="L36" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="37" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
@@ -4624,6 +4808,12 @@
       <c r="J37" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="L37" s="42" t="s">
+        <v>552</v>
+      </c>
+      <c r="M37" s="41" t="s">
+        <v>551</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
@@ -4656,6 +4846,12 @@
       <c r="J38" s="1" t="s">
         <v>154</v>
       </c>
+      <c r="L38" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="M38" s="41" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="39" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
@@ -4688,6 +4884,12 @@
       <c r="J39" s="1" t="s">
         <v>152</v>
       </c>
+      <c r="L39" s="42" t="s">
+        <v>570</v>
+      </c>
+      <c r="M39" s="41" t="s">
+        <v>571</v>
+      </c>
     </row>
     <row r="40" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
@@ -4720,6 +4922,12 @@
       <c r="J40" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="L40" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="M40" s="41" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="41" spans="1:13" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
@@ -11195,39 +11403,419 @@
         <v>152</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="241" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="242" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="243" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="244" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="245" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="246" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="247" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="248" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="249" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="250" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="251" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="252" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="253" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="254" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="255" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="256" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="257" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="258" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="259" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="260" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="261" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="262" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="263" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="264" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="265" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="266" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="267" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="268" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="269" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="270" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="271" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="272" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="240" spans="1:10" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A240" s="41" t="s">
+        <v>542</v>
+      </c>
+      <c r="B240" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D240" s="41">
+        <v>2</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A241" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B241" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D241" s="1">
+        <v>1</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F241" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A242" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B242" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D242" s="1">
+        <v>1</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A243" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B243" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D243" s="41">
+        <v>2</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A244" s="41" t="s">
+        <v>554</v>
+      </c>
+      <c r="B244" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C244" s="42" t="s">
+        <v>552</v>
+      </c>
+      <c r="D244" s="41">
+        <v>1</v>
+      </c>
+      <c r="E244" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F244" s="41" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A245" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B245" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D245" s="41">
+        <v>1</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F245" s="41" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A246" s="41" t="s">
+        <v>557</v>
+      </c>
+      <c r="B246" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D246" s="41">
+        <v>1</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F246" s="41" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A247" s="41" t="s">
+        <v>559</v>
+      </c>
+      <c r="B247" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D247" s="41">
+        <v>1</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F247" s="41" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A248" s="41" t="s">
+        <v>561</v>
+      </c>
+      <c r="B248" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D248" s="41">
+        <v>1</v>
+      </c>
+      <c r="E248" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F248" s="41" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A249" s="41" t="s">
+        <v>562</v>
+      </c>
+      <c r="B249" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D249" s="41">
+        <v>1</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F249" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A250" s="41" t="s">
+        <v>563</v>
+      </c>
+      <c r="B250" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D250" s="41">
+        <v>1</v>
+      </c>
+      <c r="E250" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F250" s="41" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A251" s="41" t="s">
+        <v>564</v>
+      </c>
+      <c r="B251" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D251" s="41">
+        <v>2</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F251" s="41" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A252" s="41" t="s">
+        <v>568</v>
+      </c>
+      <c r="B252" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="D252" s="41">
+        <v>1</v>
+      </c>
+      <c r="E252" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F252" s="41" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A253" s="41" t="s">
+        <v>572</v>
+      </c>
+      <c r="B253" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D253" s="1">
+        <v>1</v>
+      </c>
+      <c r="E253" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F253" s="41" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A254" s="41" t="s">
+        <v>576</v>
+      </c>
+      <c r="B254" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C254" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="D254" s="41">
+        <v>1</v>
+      </c>
+      <c r="E254" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F254" s="41" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A255" s="41" t="s">
+        <v>578</v>
+      </c>
+      <c r="B255" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D255" s="41">
+        <v>1</v>
+      </c>
+      <c r="E255" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F255" s="41" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A256" s="41" t="s">
+        <v>580</v>
+      </c>
+      <c r="B256" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D256" s="41">
+        <v>1</v>
+      </c>
+      <c r="E256" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F256" s="9" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A257" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B257" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D257" s="41">
+        <v>1</v>
+      </c>
+      <c r="E257" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F257" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A258" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B258" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D258" s="41">
+        <v>1</v>
+      </c>
+      <c r="E258" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F258" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A259" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B259" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D259" s="41">
+        <v>1</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="261" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="262" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="263" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="264" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="265" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="266" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="267" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="268" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="269" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="270" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="271" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="272" spans="1:6" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="273" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="274" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="275" ht="28.7" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -11277,179 +11865,204 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:A2 A230:A1048576">
-    <cfRule type="duplicateValues" dxfId="142" priority="2016"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="1611"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="1591"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="1616"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="1636"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="2041"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A140 A142:A229">
-    <cfRule type="duplicateValues" dxfId="139" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A159">
-    <cfRule type="duplicateValues" dxfId="138" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A284">
-    <cfRule type="duplicateValues" dxfId="137" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A141">
-    <cfRule type="duplicateValues" dxfId="136" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A161:A162">
-    <cfRule type="duplicateValues" dxfId="135" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A163">
-    <cfRule type="duplicateValues" dxfId="134" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A164:A165">
-    <cfRule type="duplicateValues" dxfId="133" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A166:A167">
-    <cfRule type="duplicateValues" dxfId="132" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A168:A169">
-    <cfRule type="duplicateValues" dxfId="131" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A170">
-    <cfRule type="duplicateValues" dxfId="130" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A171:A172">
-    <cfRule type="duplicateValues" dxfId="129" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A174:A175">
-    <cfRule type="duplicateValues" dxfId="128" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A188:A189">
-    <cfRule type="duplicateValues" dxfId="127" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A197:A198">
-    <cfRule type="duplicateValues" dxfId="126" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A207:A208">
-    <cfRule type="duplicateValues" dxfId="125" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A219">
-    <cfRule type="duplicateValues" dxfId="124" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A231">
-    <cfRule type="duplicateValues" dxfId="123" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A233">
-    <cfRule type="duplicateValues" dxfId="122" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A235">
-    <cfRule type="duplicateValues" dxfId="120" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A237">
-    <cfRule type="duplicateValues" dxfId="119" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A238">
-    <cfRule type="duplicateValues" dxfId="118" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A239">
-    <cfRule type="duplicateValues" dxfId="117" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="116" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="115" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="114" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="113" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="112" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B228">
-    <cfRule type="duplicateValues" dxfId="111" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B229">
-    <cfRule type="duplicateValues" dxfId="110" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="duplicateValues" dxfId="109" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H44">
-    <cfRule type="duplicateValues" dxfId="108" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H53 H40:H41 H43 H45:H47">
-    <cfRule type="duplicateValues" dxfId="107" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="duplicateValues" dxfId="106" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="378"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H62">
-    <cfRule type="duplicateValues" dxfId="105" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="373"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H74:H75">
-    <cfRule type="duplicateValues" dxfId="104" priority="1271"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="1296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H77">
-    <cfRule type="duplicateValues" dxfId="103" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="293"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H88">
-    <cfRule type="duplicateValues" dxfId="102" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="262"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H90 H86">
-    <cfRule type="duplicateValues" dxfId="101" priority="1064"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="1089"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H91">
-    <cfRule type="duplicateValues" dxfId="100" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H92">
-    <cfRule type="duplicateValues" dxfId="99" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="339"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H105">
-    <cfRule type="duplicateValues" dxfId="98" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H108">
-    <cfRule type="duplicateValues" dxfId="97" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142">
-    <cfRule type="duplicateValues" dxfId="96" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H143">
-    <cfRule type="duplicateValues" dxfId="95" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H150">
-    <cfRule type="duplicateValues" dxfId="94" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H163">
-    <cfRule type="duplicateValues" dxfId="93" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H178">
-    <cfRule type="duplicateValues" dxfId="92" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H232">
-    <cfRule type="duplicateValues" dxfId="91" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L95:L123">
-    <cfRule type="duplicateValues" dxfId="90" priority="1668"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="1693"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L40:M40 L1:M2 M3:M36">
-    <cfRule type="duplicateValues" dxfId="89" priority="1175"/>
+  <conditionalFormatting sqref="L40:M40 L1:M2 M3:M39">
+    <cfRule type="duplicateValues" dxfId="99" priority="1200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M29">
-    <cfRule type="duplicateValues" dxfId="88" priority="2005"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="2030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M31">
-    <cfRule type="duplicateValues" dxfId="87" priority="2007"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="2032"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M36">
-    <cfRule type="duplicateValues" dxfId="86" priority="2009"/>
+  <conditionalFormatting sqref="M4:M39">
+    <cfRule type="duplicateValues" dxfId="96" priority="2034"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M30:M31">
-    <cfRule type="duplicateValues" dxfId="85" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32">
-    <cfRule type="duplicateValues" dxfId="84" priority="339"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P97:P128">
-    <cfRule type="duplicateValues" dxfId="82" priority="1670"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="1695"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A241">
+    <cfRule type="duplicateValues" dxfId="91" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A241">
+    <cfRule type="duplicateValues" dxfId="90" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A242">
+    <cfRule type="duplicateValues" dxfId="89" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A245">
+    <cfRule type="duplicateValues" dxfId="87" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C254">
+    <cfRule type="duplicateValues" dxfId="86" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A257">
+    <cfRule type="duplicateValues" dxfId="85" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A258">
+    <cfRule type="duplicateValues" dxfId="84" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A259">
+    <cfRule type="duplicateValues" dxfId="83" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A282">
+    <cfRule type="duplicateValues" dxfId="0" priority="2054"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -14560,166 +15173,166 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="82" priority="88"/>
     <cfRule type="duplicateValues" dxfId="81" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="79" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="77" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32:B34">
+    <cfRule type="duplicateValues" dxfId="76" priority="82"/>
     <cfRule type="duplicateValues" dxfId="75" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="74" priority="80"/>
     <cfRule type="duplicateValues" dxfId="73" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="72" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="10"/>
     <cfRule type="duplicateValues" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="65" priority="76"/>
     <cfRule type="duplicateValues" dxfId="64" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39">
+    <cfRule type="duplicateValues" dxfId="63" priority="74"/>
     <cfRule type="duplicateValues" dxfId="62" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40">
+    <cfRule type="duplicateValues" dxfId="61" priority="70"/>
     <cfRule type="duplicateValues" dxfId="60" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="59" priority="66"/>
     <cfRule type="duplicateValues" dxfId="58" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="56" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="54" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="53" priority="62"/>
     <cfRule type="duplicateValues" dxfId="52" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
+    <cfRule type="duplicateValues" dxfId="51" priority="58"/>
     <cfRule type="duplicateValues" dxfId="50" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
+    <cfRule type="duplicateValues" dxfId="49" priority="60"/>
     <cfRule type="duplicateValues" dxfId="48" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="46" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="45" priority="52"/>
     <cfRule type="duplicateValues" dxfId="44" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="43" priority="48"/>
     <cfRule type="duplicateValues" dxfId="42" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="41" priority="50"/>
     <cfRule type="duplicateValues" dxfId="40" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="39" priority="46"/>
     <cfRule type="duplicateValues" dxfId="38" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53:B54">
-    <cfRule type="duplicateValues" dxfId="36" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
+    <cfRule type="duplicateValues" dxfId="35" priority="42"/>
     <cfRule type="duplicateValues" dxfId="34" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:B58">
+    <cfRule type="duplicateValues" dxfId="33" priority="40"/>
     <cfRule type="duplicateValues" dxfId="32" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="31" priority="38"/>
     <cfRule type="duplicateValues" dxfId="30" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="29" priority="36"/>
     <cfRule type="duplicateValues" dxfId="28" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
     <cfRule type="duplicateValues" dxfId="26" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="24" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
     <cfRule type="duplicateValues" dxfId="22" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:B66">
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
     <cfRule type="duplicateValues" dxfId="20" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67:B68">
+    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
     <cfRule type="duplicateValues" dxfId="18" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
     <cfRule type="duplicateValues" dxfId="16" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="15" priority="22"/>
     <cfRule type="duplicateValues" dxfId="14" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P8 P10">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:S1 S2:S34">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S28">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S30">
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S34">
-    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S29:S30">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31">
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
     <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -15207,13 +15820,13 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="O3:O8 O10">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O12">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
